--- a/templates/detailed_entitlement_to_shift_allowance.xlsx
+++ b/templates/detailed_entitlement_to_shift_allowance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF1C254D-A0EE-4760-B765-0D0D67D27D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C0FD3F-DB20-4594-949E-E05C90D02D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" tabRatio="325" xr2:uid="{7F4F08CC-EE4F-4293-870C-47068A1A5ED8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="325" xr2:uid="{7F4F08CC-EE4F-4293-870C-47068A1A5ED8}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -64,17 +64,17 @@
     </r>
   </si>
   <si>
-    <t>Hora de Entrada</t>
+    <t>Data</t>
   </si>
   <si>
-    <t>Data</t>
+    <t>Hora de Entrada</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,22 +130,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0" tint="-0.499984740745262"/>
+      <u/>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -165,7 +158,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -267,6 +260,32 @@
       </top>
       <bottom style="thin">
         <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
       </bottom>
       <diagonal/>
     </border>
@@ -298,11 +317,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -316,29 +335,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -356,13 +360,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>292102</xdr:colOff>
+      <xdr:colOff>165102</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>190022</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>812800</xdr:colOff>
+      <xdr:colOff>685800</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>187358</xdr:rowOff>
     </xdr:to>
@@ -393,7 +397,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="482602" y="190022"/>
+          <a:off x="355602" y="190022"/>
           <a:ext cx="520698" cy="568836"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -751,10 +755,10 @@
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>1</v>
@@ -763,285 +767,311 @@
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="11"/>
       <c r="C10" s="12"/>
-      <c r="D10" s="9"/>
+      <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
-      <c r="D11" s="9"/>
+      <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
-      <c r="D12" s="9"/>
+      <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
-      <c r="D13" s="9"/>
+      <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="11"/>
       <c r="C14" s="12"/>
-      <c r="D14" s="9"/>
+      <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="11"/>
       <c r="C15" s="12"/>
-      <c r="D15" s="9"/>
+      <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="11"/>
       <c r="C16" s="12"/>
-      <c r="D16" s="9"/>
+      <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="11"/>
       <c r="C17" s="12"/>
-      <c r="D17" s="9"/>
+      <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="11"/>
       <c r="C18" s="12"/>
-      <c r="D18" s="9"/>
+      <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="11"/>
       <c r="C19" s="12"/>
-      <c r="D19" s="9"/>
+      <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="11"/>
       <c r="C20" s="12"/>
-      <c r="D20" s="9"/>
+      <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="11"/>
       <c r="C21" s="12"/>
-      <c r="D21" s="9"/>
+      <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="11"/>
       <c r="C22" s="12"/>
-      <c r="D22" s="9"/>
+      <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="11"/>
       <c r="C23" s="12"/>
-      <c r="D23" s="9"/>
+      <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="11"/>
       <c r="C24" s="12"/>
-      <c r="D24" s="9"/>
+      <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="11"/>
       <c r="C25" s="12"/>
-      <c r="D25" s="9"/>
+      <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="11"/>
       <c r="C26" s="12"/>
-      <c r="D26" s="9"/>
+      <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="11"/>
       <c r="C27" s="12"/>
-      <c r="D27" s="9"/>
+      <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="11"/>
       <c r="C28" s="12"/>
-      <c r="D28" s="9"/>
+      <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="11"/>
       <c r="C29" s="12"/>
-      <c r="D29" s="9"/>
+      <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="11"/>
       <c r="C30" s="12"/>
-      <c r="D30" s="9"/>
+      <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="11"/>
       <c r="C31" s="12"/>
-      <c r="D31" s="9"/>
+      <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="11"/>
       <c r="C32" s="12"/>
-      <c r="D32" s="9"/>
+      <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="11"/>
       <c r="C33" s="12"/>
-      <c r="D33" s="9"/>
+      <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="11"/>
       <c r="C34" s="12"/>
-      <c r="D34" s="9"/>
+      <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="11"/>
       <c r="C35" s="12"/>
-      <c r="D35" s="9"/>
+      <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" s="11"/>
       <c r="C36" s="12"/>
-      <c r="D36" s="9"/>
+      <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="11"/>
       <c r="C37" s="12"/>
-      <c r="D37" s="9"/>
+      <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="11"/>
       <c r="C38" s="12"/>
-      <c r="D38" s="9"/>
+      <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39" s="11"/>
       <c r="C39" s="12"/>
-      <c r="D39" s="9"/>
+      <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="11"/>
       <c r="C40" s="12"/>
-      <c r="D40" s="9"/>
+      <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41" s="11"/>
       <c r="C41" s="12"/>
-      <c r="D41" s="9"/>
+      <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B42" s="11"/>
       <c r="C42" s="12"/>
-      <c r="D42" s="9"/>
+      <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B43" s="11"/>
       <c r="C43" s="12"/>
-      <c r="D43" s="9"/>
+      <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B44" s="11"/>
       <c r="C44" s="12"/>
-      <c r="D44" s="9"/>
+      <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B45" s="11"/>
       <c r="C45" s="12"/>
-      <c r="D45" s="9"/>
+      <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B46" s="11"/>
       <c r="C46" s="12"/>
-      <c r="D46" s="9"/>
+      <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B47" s="11"/>
       <c r="C47" s="12"/>
-      <c r="D47" s="9"/>
+      <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B48" s="11"/>
       <c r="C48" s="12"/>
-      <c r="D48" s="9"/>
+      <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B49" s="11"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="10"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B49:C49"/>
     <mergeCell ref="B6:F7"/>
     <mergeCell ref="B44:C44"/>
@@ -1058,61 +1088,10 @@
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
   </mergeCells>
-  <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="F10:F49">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{913DBBC9-D456-4DFA-A976-F4E584A2265E}">
-            <xm:f>NOT(ISERROR(SEARCH("VERIFICAÇÃO",F10)))</xm:f>
-            <xm:f>"VERIFICAÇÃO"</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i val="0"/>
-                <color rgb="FFFF0000"/>
-              </font>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>F10:F49</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
 </worksheet>
 </file>